--- a/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
+++ b/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 134,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▲ 52,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 1000,0%</t>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1000,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -811,9 +811,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -881,12 +881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -899,15 +899,15 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -967,20 +967,20 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -990,21 +990,21 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,10 +1035,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1047,39 +1045,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1228,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1690,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1844,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1921,12 +1917,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1998,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2075,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,12 +2148,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2229,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2306,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2383,12 +2379,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2460,12 +2456,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2537,12 +2533,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2614,12 +2610,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2691,12 +2687,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2768,12 +2764,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2845,12 +2841,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2922,12 +2918,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2999,12 +2995,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3076,12 +3072,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3153,12 +3149,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3230,12 +3226,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3307,12 +3303,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3384,12 +3380,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,12 +3457,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3538,12 +3534,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3615,12 +3611,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3692,12 +3688,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3769,12 +3765,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3846,12 +3842,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3923,12 +3919,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4000,12 +3996,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4077,12 +4073,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4154,12 +4150,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4231,12 +4227,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4308,12 +4304,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4385,12 +4381,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4462,12 +4458,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4539,12 +4535,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4616,12 +4612,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4693,12 +4689,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4770,12 +4766,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4847,12 +4843,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4924,12 +4920,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5001,12 +4997,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5078,12 +5074,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5155,12 +5151,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5232,12 +5228,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5309,12 +5305,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5386,12 +5382,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5463,12 +5459,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5540,12 +5536,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5617,12 +5613,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5694,12 +5690,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5771,12 +5767,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5848,12 +5844,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5925,12 +5921,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6002,12 +5998,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6079,12 +6075,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6156,12 +6152,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6233,12 +6229,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6310,12 +6306,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6387,12 +6383,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6464,12 +6460,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6541,12 +6537,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6618,12 +6614,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6695,12 +6691,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6772,12 +6768,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6849,12 +6845,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6926,82 +6922,159 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-034</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Organizador duplo giratorio Multiuso</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>6978059012</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
+++ b/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 134,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 52,6%</t>
+        <v>43</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 134,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 72,7%</t>
+        <v>29</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,6%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1000,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1000,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -884,9 +884,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -954,12 +954,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -972,15 +972,15 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1040,20 +1040,20 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1063,21 +1063,21 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,10 +1108,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1120,39 +1118,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1224,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1301,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1378,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,12 +1451,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1840,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1917,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1994,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2071,12 +2067,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2148,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2225,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,12 +2298,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2379,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2456,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2533,12 +2529,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2610,12 +2606,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2687,12 +2683,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2764,12 +2760,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2841,12 +2837,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2918,12 +2914,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2995,12 +2991,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3072,12 +3068,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3149,12 +3145,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3226,12 +3222,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3303,12 +3299,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3380,12 +3376,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3457,12 +3453,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3534,12 +3530,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3611,12 +3607,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3688,12 +3684,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3765,12 +3761,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3842,12 +3838,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3919,12 +3915,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3996,12 +3992,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4073,12 +4069,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4150,12 +4146,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4227,12 +4223,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4304,12 +4300,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4381,12 +4377,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4458,12 +4454,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4535,12 +4531,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4612,12 +4608,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4689,12 +4685,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4766,12 +4762,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4843,12 +4839,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4920,12 +4916,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4997,12 +4993,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5074,12 +5070,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5151,12 +5147,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5228,12 +5224,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5305,12 +5301,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5382,12 +5378,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5459,12 +5455,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5536,12 +5532,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5613,12 +5609,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5690,12 +5686,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5767,12 +5763,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5844,12 +5840,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5921,12 +5917,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5998,12 +5994,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6075,12 +6071,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6152,12 +6148,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6229,12 +6225,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6306,12 +6302,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6383,12 +6379,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6460,12 +6456,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6537,12 +6533,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6614,12 +6610,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6691,12 +6687,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6768,12 +6764,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6845,12 +6841,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6922,12 +6918,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6999,82 +6995,159 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>UTD-034</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Organizador duplo giratorio Multiuso</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>6978059012</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O86"/>
+  <autoFilter ref="A1:O87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
+++ b/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 67,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,3%</t>
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 134,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▲ 52,6%</t>
+          <t>▲ 48,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 134,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▲ 52,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 1000,0%</t>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1000,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -957,9 +957,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1045,15 +1045,15 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,21 +1136,21 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-034</t>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1181,10 +1181,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1193,39 +1191,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1297,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1374,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1451,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1528,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,12 +1601,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1990,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2144,12 +2140,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2221,12 +2217,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2298,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2375,12 +2371,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2448,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2529,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2606,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2683,12 +2679,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2760,12 +2756,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2837,12 +2833,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2914,12 +2910,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2991,12 +2987,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3068,12 +3064,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3145,12 +3141,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3222,12 +3218,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3299,12 +3295,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3376,12 +3372,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3453,12 +3449,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3530,12 +3526,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3607,12 +3603,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3684,12 +3680,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3761,12 +3757,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3838,12 +3834,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3915,12 +3911,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3992,12 +3988,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4069,12 +4065,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4146,12 +4142,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4223,12 +4219,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4300,12 +4296,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4377,12 +4373,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4454,12 +4450,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,12 +4527,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4608,12 +4604,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4681,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4762,12 +4758,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,12 +4835,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4916,12 +4912,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4993,12 +4989,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5070,12 +5066,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5147,12 +5143,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5224,12 +5220,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5301,12 +5297,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5378,12 +5374,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5455,12 +5451,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5532,12 +5528,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5609,12 +5605,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5686,12 +5682,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5763,12 +5759,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5840,12 +5836,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5917,12 +5913,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5994,12 +5990,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6071,12 +6067,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6148,12 +6144,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6225,12 +6221,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6302,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6379,12 +6375,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6456,12 +6452,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6533,12 +6529,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6610,12 +6606,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6687,12 +6683,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6764,12 +6760,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6841,12 +6837,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6918,12 +6914,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6995,12 +6991,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7072,82 +7068,159 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>UTD-034</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Organizador duplo giratorio Multiuso</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>6978059012</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O87"/>
+  <autoFilter ref="A1:O88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
+++ b/saida_skus/SKU_UTD-034-ORGANIZADOR-DUPLO-GIRATORIO-MULTIUSO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,25 +589,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 67,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 75,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,3%</t>
+          <t>▼ 25,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 134,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 134,00</t>
+          <t>R$ 67,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 52,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▲ 105,6%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 67,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1000,0%</t>
+        <v>36</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>43</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 134,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 52,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 75,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1000,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,59 +1319,55 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 75,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,51 +1400,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1485,10 +1473,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1497,39 +1483,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1601,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1678,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1893,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1986,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2047,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2140,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2217,12 +2201,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2294,12 +2278,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2371,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2448,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2525,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,12 +2586,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2679,12 +2663,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2756,12 +2740,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2833,12 +2817,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2910,12 +2894,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2987,12 +2971,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3064,12 +3048,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3141,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3218,12 +3202,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3295,12 +3279,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3372,12 +3356,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3449,12 +3433,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3526,12 +3510,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3603,12 +3587,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3680,12 +3664,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3757,12 +3741,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3834,12 +3818,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3911,12 +3895,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3988,12 +3972,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4065,12 +4049,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4142,12 +4126,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4219,12 +4203,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4296,12 +4280,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4373,12 +4357,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4450,12 +4434,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4527,12 +4511,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4604,12 +4588,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4681,12 +4665,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4758,12 +4742,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4835,12 +4819,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4912,12 +4896,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4989,12 +4973,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5066,12 +5050,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5143,12 +5127,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5220,12 +5204,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5297,12 +5281,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5374,12 +5358,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5451,12 +5435,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5528,12 +5512,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5605,12 +5589,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5682,12 +5666,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5759,12 +5743,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5836,12 +5820,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5913,12 +5897,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5990,12 +5974,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6067,12 +6051,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6144,12 +6128,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6221,12 +6205,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6298,12 +6282,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6375,12 +6359,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6452,12 +6436,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6529,12 +6513,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6606,12 +6590,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6683,12 +6667,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6760,12 +6744,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6837,12 +6821,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6914,12 +6898,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6991,12 +6975,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7068,12 +7052,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7145,82 +7129,390 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>UTD-034</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Organizador duplo giratorio Multiuso</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>6978059012</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-034</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Organizador duplo giratorio Multiuso</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6978059012</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O88"/>
+  <autoFilter ref="A1:O92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>